--- a/diseases/d178/2015-2019.xlsx
+++ b/diseases/d178/2015-2019.xlsx
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -12662,7 +12662,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -18226,7 +18226,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21632,7 +21632,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -23938,7 +23938,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24742,7 +24742,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27344,7 +27344,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28550,7 +28550,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30454,7 +30454,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30856,7 +30856,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -31554,7 +31554,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31956,7 +31956,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32358,7 +32358,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32760,7 +32760,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -33458,7 +33458,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34262,7 +34262,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -35362,7 +35362,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35764,7 +35764,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36568,7 +36568,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -36970,7 +36970,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -38070,7 +38070,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38472,7 +38472,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38874,7 +38874,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39572,7 +39572,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -39974,7 +39974,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -40376,7 +40376,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40778,7 +40778,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -41328,7 +41328,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -41878,7 +41878,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -42280,7 +42280,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -42682,7 +42682,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -43084,7 +43084,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43782,7 +43782,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44184,7 +44184,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -44988,7 +44988,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45686,7 +45686,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -46088,7 +46088,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46490,7 +46490,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -47992,7 +47992,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48394,7 +48394,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48796,7 +48796,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -49198,7 +49198,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">

--- a/diseases/d178/2015-2019.xlsx
+++ b/diseases/d178/2015-2019.xlsx
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -12662,7 +12662,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -18226,7 +18226,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21632,7 +21632,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -23938,7 +23938,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24742,7 +24742,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27344,7 +27344,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28550,7 +28550,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30454,7 +30454,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30856,7 +30856,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -31554,7 +31554,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31956,7 +31956,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32358,7 +32358,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32760,7 +32760,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -33458,7 +33458,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34262,7 +34262,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -35362,7 +35362,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35764,7 +35764,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36568,7 +36568,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -36970,7 +36970,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -38070,7 +38070,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38472,7 +38472,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38874,7 +38874,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39572,7 +39572,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -39974,7 +39974,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -40376,7 +40376,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40778,7 +40778,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -41328,7 +41328,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -41878,7 +41878,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -42280,7 +42280,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -42682,7 +42682,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -43084,7 +43084,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43782,7 +43782,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44184,7 +44184,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -44988,7 +44988,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45686,7 +45686,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -46088,7 +46088,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46490,7 +46490,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -47992,7 +47992,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48394,7 +48394,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48796,7 +48796,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -49198,7 +49198,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">

--- a/diseases/d178/2015-2019.xlsx
+++ b/diseases/d178/2015-2019.xlsx
@@ -8760,9 +8760,6 @@
       <c r="P56" t="n">
         <v>3</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.002363815981417097</v>
       </c>
@@ -9012,7 +9009,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -9162,9 +9159,6 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9414,7 +9408,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -9564,9 +9558,6 @@
       <c r="P60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.0007879386604723656</v>
       </c>
@@ -9816,7 +9807,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -9966,9 +9957,6 @@
       <c r="P62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.0007879386604723656</v>
       </c>
@@ -10218,7 +10206,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -10664,9 +10652,6 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -10916,7 +10901,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -11066,9 +11051,6 @@
       <c r="P68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.0007879386604723656</v>
       </c>
@@ -11318,7 +11300,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -11468,9 +11450,6 @@
       <c r="P70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.0007879386604723656</v>
       </c>
@@ -11720,7 +11699,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -11870,9 +11849,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12122,7 +12098,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -12420,9 +12396,6 @@
       <c r="P75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12672,7 +12645,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -12970,9 +12943,6 @@
       <c r="P78" t="n">
         <v>3</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.002363815981417097</v>
       </c>
@@ -13222,7 +13192,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -13372,9 +13342,6 @@
       <c r="P80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -13624,7 +13591,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -13774,9 +13741,6 @@
       <c r="P82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14026,7 +13990,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -14176,9 +14140,6 @@
       <c r="P84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -14428,7 +14389,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -14874,9 +14835,6 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -15126,7 +15084,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -15276,9 +15234,6 @@
       <c r="P90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.0007879386604723656</v>
       </c>
@@ -15528,7 +15483,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -15678,9 +15633,6 @@
       <c r="P92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -15930,7 +15882,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -16080,9 +16032,6 @@
       <c r="P94" t="n">
         <v>5</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.003939693302361828</v>
       </c>
@@ -16332,7 +16281,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -16778,9 +16727,6 @@
       <c r="P98" t="n">
         <v>3</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.002363815981417097</v>
       </c>
@@ -17030,7 +16976,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -17180,9 +17126,6 @@
       <c r="P100" t="n">
         <v>2</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.001575877320944731</v>
       </c>
@@ -17432,7 +17375,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -17582,9 +17525,6 @@
       <c r="P102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.0007879386604723656</v>
       </c>
@@ -17834,7 +17774,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -17984,9 +17924,6 @@
       <c r="P104" t="n">
         <v>2</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.001575877320944731</v>
       </c>
@@ -18236,7 +18173,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -18386,9 +18323,6 @@
       <c r="P106" t="n">
         <v>3</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.002363815981417097</v>
       </c>
@@ -18638,7 +18572,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -19084,9 +19018,6 @@
       <c r="P110" t="n">
         <v>4</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.003151754641889462</v>
       </c>
@@ -19336,7 +19267,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -19486,9 +19417,6 @@
       <c r="P112" t="n">
         <v>5</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.003939693302361828</v>
       </c>
@@ -19738,7 +19666,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -19888,9 +19816,6 @@
       <c r="P114" t="n">
         <v>10</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.007879386604723657</v>
       </c>
@@ -20140,7 +20065,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -20290,9 +20215,6 @@
       <c r="P116" t="n">
         <v>9</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.007091447944251291</v>
       </c>
@@ -20542,7 +20464,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -20988,9 +20910,6 @@
       <c r="P120" t="n">
         <v>10</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.007879386604723657</v>
       </c>
@@ -21240,7 +21159,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -21390,9 +21309,6 @@
       <c r="P122" t="n">
         <v>10</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.007879386604723657</v>
       </c>
@@ -21642,7 +21558,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -21792,9 +21708,6 @@
       <c r="P124" t="n">
         <v>4</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.003151754641889462</v>
       </c>
@@ -22044,7 +21957,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -22194,9 +22107,6 @@
       <c r="P126" t="n">
         <v>5</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.003939693302361828</v>
       </c>
@@ -22446,7 +22356,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -22892,9 +22802,6 @@
       <c r="P130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.0007879386604723656</v>
       </c>
@@ -23144,7 +23051,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -23294,9 +23201,6 @@
       <c r="P132" t="n">
         <v>3</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.002363815981417097</v>
       </c>
@@ -23546,7 +23450,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -23696,9 +23600,6 @@
       <c r="P134" t="n">
         <v>5</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.003939693302361828</v>
       </c>
@@ -23948,7 +23849,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -24098,9 +23999,6 @@
       <c r="P136" t="n">
         <v>2</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.001575877320944731</v>
       </c>
@@ -24350,7 +24248,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -24500,9 +24398,6 @@
       <c r="P138" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.0007879386604723656</v>
       </c>
@@ -24752,7 +24647,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -25198,9 +25093,6 @@
       <c r="P142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -25450,7 +25342,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -25600,9 +25492,6 @@
       <c r="P144" t="n">
         <v>3</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.002367808721718454</v>
       </c>
@@ -25852,7 +25741,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -26002,9 +25891,6 @@
       <c r="P146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -26254,7 +26140,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -26404,9 +26290,6 @@
       <c r="P148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -26656,7 +26539,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -27102,9 +26985,6 @@
       <c r="P152" t="n">
         <v>1</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -27354,7 +27234,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -27504,9 +27384,6 @@
       <c r="P154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -27756,7 +27633,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -27906,9 +27783,6 @@
       <c r="P156" t="n">
         <v>2</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.001578539147812302</v>
       </c>
@@ -28158,7 +28032,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -28308,9 +28182,6 @@
       <c r="P158" t="n">
         <v>1</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -28560,7 +28431,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -29006,9 +28877,6 @@
       <c r="P162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -29258,7 +29126,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -29408,9 +29276,6 @@
       <c r="P164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -29660,7 +29525,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -29810,9 +29675,6 @@
       <c r="P166" t="n">
         <v>1</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -30062,7 +29924,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -30212,9 +30074,6 @@
       <c r="P168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -30464,7 +30323,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -30614,9 +30473,6 @@
       <c r="P170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -30866,7 +30722,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -31312,9 +31168,6 @@
       <c r="P174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -31564,7 +31417,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -31714,9 +31567,6 @@
       <c r="P176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -31966,7 +31816,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -32116,9 +31966,6 @@
       <c r="P178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -32368,7 +32215,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -32518,9 +32365,6 @@
       <c r="P180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -32770,7 +32614,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -33216,9 +33060,6 @@
       <c r="P184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -33468,7 +33309,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -33618,9 +33459,6 @@
       <c r="P186" t="n">
         <v>2</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.001578539147812302</v>
       </c>
@@ -33870,7 +33708,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -34020,9 +33858,6 @@
       <c r="P188" t="n">
         <v>1</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -34272,7 +34107,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -34422,9 +34257,6 @@
       <c r="P190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -34674,7 +34506,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -35120,9 +34952,6 @@
       <c r="P194" t="n">
         <v>3</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.002367808721718454</v>
       </c>
@@ -35372,7 +35201,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -35522,9 +35351,6 @@
       <c r="P196" t="n">
         <v>2</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.001578539147812302</v>
       </c>
@@ -35774,7 +35600,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -35924,9 +35750,6 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -36176,7 +35999,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -36326,9 +36149,6 @@
       <c r="P200" t="n">
         <v>1</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -36578,7 +36398,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -36728,9 +36548,6 @@
       <c r="P202" t="n">
         <v>1</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -36980,7 +36797,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -37426,9 +37243,6 @@
       <c r="P206" t="n">
         <v>2</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.001578539147812302</v>
       </c>
@@ -37678,7 +37492,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -37828,9 +37642,6 @@
       <c r="P208" t="n">
         <v>1</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -38080,7 +37891,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -38230,9 +38041,6 @@
       <c r="P210" t="n">
         <v>4</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.003157078295624605</v>
       </c>
@@ -38482,7 +38290,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -38632,9 +38440,6 @@
       <c r="P212" t="n">
         <v>3</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.002367808721718454</v>
       </c>
@@ -38884,7 +38689,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -39330,9 +39135,6 @@
       <c r="P216" t="n">
         <v>1</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -39582,7 +39384,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -39732,9 +39534,6 @@
       <c r="P218" t="n">
         <v>1</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -39984,7 +39783,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -40134,9 +39933,6 @@
       <c r="P220" t="n">
         <v>1</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -40386,7 +40182,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -40536,9 +40332,6 @@
       <c r="P222" t="n">
         <v>1</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -40788,7 +40581,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -41086,9 +40879,6 @@
       <c r="P225" t="n">
         <v>2</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.001578539147812302</v>
       </c>
@@ -41338,7 +41128,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -41636,9 +41426,6 @@
       <c r="P228" t="n">
         <v>2</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.001578539147812302</v>
       </c>
@@ -41888,7 +41675,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -42038,9 +41825,6 @@
       <c r="P230" t="n">
         <v>1</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -42290,7 +42074,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -42440,9 +42224,6 @@
       <c r="P232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -42692,7 +42473,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -42842,9 +42623,6 @@
       <c r="P234" t="n">
         <v>2</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.001578539147812302</v>
       </c>
@@ -43094,7 +42872,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -43540,9 +43318,6 @@
       <c r="P238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -43792,7 +43567,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -43942,9 +43717,6 @@
       <c r="P240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -44194,7 +43966,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -44344,9 +44116,6 @@
       <c r="P242" t="n">
         <v>1</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -44596,7 +44365,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -44746,9 +44515,6 @@
       <c r="P244" t="n">
         <v>1</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -44998,7 +44764,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -45444,9 +45210,6 @@
       <c r="P248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -45696,7 +45459,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -45846,9 +45609,6 @@
       <c r="P250" t="n">
         <v>1</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -46098,7 +45858,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -46248,9 +46008,6 @@
       <c r="P252" t="n">
         <v>1</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -46500,7 +46257,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -46650,9 +46407,6 @@
       <c r="P254" t="n">
         <v>4</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.003157078295624605</v>
       </c>
@@ -46902,7 +46656,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -47200,9 +46954,6 @@
       <c r="P257" t="n">
         <v>3</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.002367808721718454</v>
       </c>
@@ -47452,7 +47203,7 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -47750,9 +47501,6 @@
       <c r="P260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0</v>
       </c>
@@ -48002,7 +47750,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -48152,9 +47900,6 @@
       <c r="P262" t="n">
         <v>2</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.001578539147812302</v>
       </c>
@@ -48404,7 +48149,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -48554,9 +48299,6 @@
       <c r="P264" t="n">
         <v>1</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.0007892695739061512</v>
       </c>
@@ -48806,7 +48548,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -48956,9 +48698,6 @@
       <c r="P266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
@@ -49208,7 +48947,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN267" t="b">

--- a/diseases/d178/2015-2019.xlsx
+++ b/diseases/d178/2015-2019.xlsx
@@ -8999,7 +8999,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18562,7 +18562,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19656,7 +19656,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -20055,7 +20055,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -21947,7 +21947,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24637,7 +24637,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27224,7 +27224,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -27623,7 +27623,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -31407,7 +31407,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31806,7 +31806,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32205,7 +32205,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32604,7 +32604,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -33299,7 +33299,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33698,7 +33698,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34097,7 +34097,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34496,7 +34496,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -35191,7 +35191,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35590,7 +35590,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -35989,7 +35989,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36388,7 +36388,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -36787,7 +36787,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -37482,7 +37482,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -37881,7 +37881,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38280,7 +38280,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38679,7 +38679,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39374,7 +39374,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -39773,7 +39773,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -40172,7 +40172,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40571,7 +40571,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -41118,7 +41118,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -41665,7 +41665,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -42064,7 +42064,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -42463,7 +42463,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -42862,7 +42862,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43557,7 +43557,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -43956,7 +43956,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -44355,7 +44355,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -44754,7 +44754,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45449,7 +45449,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -45848,7 +45848,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46247,7 +46247,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -46646,7 +46646,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -47193,7 +47193,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -47740,7 +47740,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48139,7 +48139,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48538,7 +48538,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -48937,7 +48937,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">

--- a/diseases/d178/2015-2019.xlsx
+++ b/diseases/d178/2015-2019.xlsx
@@ -8999,7 +8999,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18562,7 +18562,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19656,7 +19656,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -20055,7 +20055,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -21947,7 +21947,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24637,7 +24637,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27224,7 +27224,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -27623,7 +27623,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -31407,7 +31407,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31806,7 +31806,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32205,7 +32205,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32604,7 +32604,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -33299,7 +33299,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33698,7 +33698,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34097,7 +34097,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34496,7 +34496,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -35191,7 +35191,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35590,7 +35590,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -35989,7 +35989,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36388,7 +36388,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -36787,7 +36787,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -37482,7 +37482,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -37881,7 +37881,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38280,7 +38280,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38679,7 +38679,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39374,7 +39374,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -39773,7 +39773,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -40172,7 +40172,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40571,7 +40571,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -41118,7 +41118,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -41665,7 +41665,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -42064,7 +42064,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -42463,7 +42463,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -42862,7 +42862,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43557,7 +43557,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -43956,7 +43956,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -44355,7 +44355,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -44754,7 +44754,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45449,7 +45449,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -45848,7 +45848,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46247,7 +46247,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -46646,7 +46646,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -47193,7 +47193,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -47740,7 +47740,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48139,7 +48139,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48538,7 +48538,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -48937,7 +48937,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">

--- a/diseases/d178/2015-2019.xlsx
+++ b/diseases/d178/2015-2019.xlsx
@@ -8999,7 +8999,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18562,7 +18562,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -19656,7 +19656,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -20055,7 +20055,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -21947,7 +21947,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24637,7 +24637,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27224,7 +27224,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -27623,7 +27623,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -31407,7 +31407,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31806,7 +31806,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32205,7 +32205,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32604,7 +32604,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -33299,7 +33299,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33698,7 +33698,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34097,7 +34097,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34496,7 +34496,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -35191,7 +35191,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35590,7 +35590,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -35989,7 +35989,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36388,7 +36388,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -36787,7 +36787,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -37482,7 +37482,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -37881,7 +37881,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38280,7 +38280,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38679,7 +38679,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39374,7 +39374,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -39773,7 +39773,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -40172,7 +40172,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40571,7 +40571,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -41118,7 +41118,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -41665,7 +41665,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -42064,7 +42064,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -42463,7 +42463,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -42862,7 +42862,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43557,7 +43557,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -43956,7 +43956,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -44355,7 +44355,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -44754,7 +44754,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45449,7 +45449,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -45848,7 +45848,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46247,7 +46247,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -46646,7 +46646,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -47193,7 +47193,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -47740,7 +47740,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48139,7 +48139,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48538,7 +48538,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -48937,7 +48937,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
